--- a/Config/Luban/source/TbWeapon.xlsx
+++ b/Config/Luban/source/TbWeapon.xlsx
@@ -1,344 +1,193 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XPHUNITY\ProjectSplatoon\Config\Luban\source\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weapon" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>prefabAddress</t>
-  </si>
-  <si>
-    <t>fireRate</t>
-  </si>
-  <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>shotInk</t>
-  </si>
-  <si>
-    <t>speedMin</t>
-  </si>
-  <si>
-    <t>speedMax</t>
-  </si>
-  <si>
-    <t>gravity</t>
-  </si>
-  <si>
-    <t>lifetime</t>
-  </si>
-  <si>
-    <t>collisionRadius</t>
-  </si>
-  <si>
-    <t>spreadDegrees</t>
-  </si>
-  <si>
-    <t>paintRadiusMin</t>
-  </si>
-  <si>
-    <t>paintRadiusMax</t>
-  </si>
-  <si>
-    <t>paintHardness</t>
-  </si>
-  <si>
-    <t>paintStrength</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>武器 ID</t>
-  </si>
-  <si>
-    <t>武器名称</t>
-  </si>
-  <si>
-    <t>正式武器地址</t>
-  </si>
-  <si>
-    <t>权威射速（发/秒）</t>
-  </si>
-  <si>
-    <t>每颗伤害</t>
-  </si>
-  <si>
-    <t>每颗耗墨</t>
-  </si>
-  <si>
-    <t>最低初速（米/秒）</t>
-  </si>
-  <si>
-    <t>最高初速（米/秒）</t>
-  </si>
-  <si>
-    <t>墨弹重力（米/秒²）</t>
-  </si>
-  <si>
-    <t>有效寿命（秒）</t>
-  </si>
-  <si>
-    <t>扫掠半径（米）</t>
-  </si>
-  <si>
-    <t>散布半角（度）</t>
-  </si>
-  <si>
-    <t>最小涂色半径（米）</t>
-  </si>
-  <si>
-    <t>最大涂色半径（米）</t>
-  </si>
-  <si>
-    <t>笔刷硬度（0 到 1）</t>
-  </si>
-  <si>
-    <t>笔刷强度（0 到 1）</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Splattershot</t>
-  </si>
-  <si>
-    <t>Weapon/Splattershot</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="23">
     <font>
-      <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -650,162 +499,163 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1052,7 +902,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1061,7 +911,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1074,11 +924,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1275,232 +1188,657 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Q4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="17" width="22" customWidth="1"/>
+    <col width="22" customWidth="1" style="4" min="1" max="17"/>
+    <col width="28" customWidth="1" style="4" min="18" max="18"/>
+    <col width="28" customWidth="1" style="4" min="19" max="19"/>
+    <col width="28" customWidth="1" style="4" min="20" max="20"/>
+    <col width="28" customWidth="1" style="4" min="21" max="21"/>
+    <col width="28" customWidth="1" style="4" min="22" max="22"/>
+    <col width="28" customWidth="1" style="4" min="23" max="23"/>
+    <col width="28" customWidth="1" style="4" min="24" max="24"/>
+    <col width="28" customWidth="1" style="4" min="25" max="25"/>
+    <col width="28" customWidth="1" style="4" min="26" max="26"/>
+    <col width="28" customWidth="1" style="4" min="27" max="27"/>
+    <col width="28" customWidth="1" style="4" min="28" max="28"/>
+    <col width="28" customWidth="1" style="4" min="29" max="29"/>
+    <col width="28" customWidth="1" style="4" min="30" max="30"/>
+    <col width="28" customWidth="1" style="4" min="31" max="31"/>
+    <col width="28" customWidth="1" style="4" min="32" max="32"/>
+    <col width="28" customWidth="1" style="4" min="33" max="33"/>
+    <col width="28" customWidth="1" style="4" min="34" max="34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" spans="1:17">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="14.5" customHeight="1" s="4">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>prefabAddress</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fireRate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>shotInk</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>speedMin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>speedMax</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>gravity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lifetime</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>collisionRadius</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>spreadDegrees</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>paintRadiusMin</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>paintRadiusMax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>paintHardness</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>paintStrength</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>fireIntervalFrames</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>startFrames</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>emergeStartFrames</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>inkRecoverLockFrames</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>damageMin</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>damageReduceStartFrames</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>damageReduceEndFrames</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>straightFrames</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>brakeFrames</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>brakeSpeedMultiplier</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>jumpSpreadDegrees</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>spreadRecoverFrames</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>trailSpacing</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>trailRadius</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>trailMaxDrop</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>effectiveRange</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>paintRange</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.5" customHeight="1" s="4">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AC2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AD2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AE2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AF2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AH2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1" s="4">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>武器 ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>武器名称</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>正式武器地址</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>权威射速（发/秒）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>每颗伤害</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>每颗耗墨</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>最低初速（米/秒）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>最高初速（米/秒）</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>墨弹重力（米/秒²）</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>有效寿命（秒）</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>扫掠半径（米）</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>散布半角（度）</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>最小涂色半径（米）</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>最大涂色半径（米）</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>笔刷硬度（0 到 1）</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>笔刷强度（0 到 1）</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>连发间隔（60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>人形起手（60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>出墨起手（60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>最后一发后回墨锁定（60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>衰减后伤害（HP）</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>伤害衰减开始（飞行60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>伤害衰减结束（飞行60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>直行阶段（60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>减速过渡（60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>减速后的速度比例</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>跳跃散布半角（度）</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>落地散布恢复（60Hz参考帧）</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>沿途落墨间隔（米）</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>沿途落墨笔刷半径（米）</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>沿途落墨向下探测范围（米）</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>伤害弹最大前向射程（本项目米）</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>水平瞄准涂地射程目标（本项目米）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1" s="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RifleGirlRifle</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Weapon/RifleGirlRifle</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="T4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="Z4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="AA4" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" ht="14.5" spans="1:17">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1" spans="1:17">
-      <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" ht="14.5" spans="1:17">
-      <c r="A4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RifleGirlRifle</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Weapon/RifleGirlRifle</t>
-        </is>
-      </c>
-      <c r="E4" s="3">
-        <v>40</v>
-      </c>
-      <c r="F4" s="3">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H4" s="3">
-        <v>20</v>
-      </c>
-      <c r="I4" s="3">
-        <v>32</v>
-      </c>
-      <c r="J4" s="3">
-        <v>9.8</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0.025</v>
-      </c>
-      <c r="M4" s="3">
-        <v>5</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="O4" s="3">
-        <v>2</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>1</v>
+      <c r="AC4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>13.6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Luban/source/TbWeapon.xlsx
+++ b/Config/Luban/source/TbWeapon.xlsx
@@ -2112,7 +2112,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>26</v>
@@ -2154,7 +2154,7 @@
         <v>10</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V5" s="4" t="n">
         <v>12</v>
@@ -2256,13 +2256,13 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>52</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>34</v>
@@ -2295,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S6" s="4" t="n">
         <v>2</v>
@@ -2412,7 +2412,7 @@
         <v>34</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>33</v>
@@ -2454,7 +2454,7 @@
         <v>10</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>17</v>
@@ -2559,7 +2559,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>8</v>
